--- a/docs/xlsx/jobs-2026-10-12.xlsx
+++ b/docs/xlsx/jobs-2026-10-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="500">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1489 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Assistant Area Wildlife Manager (Wildlife Biologist 2)</t>
+  </si>
+  <si>
+    <t>Alaska Department of Fish and Game - Division of Wildlife Conservation</t>
+  </si>
+  <si>
+    <t>Dillingham, AK</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$6,841.50 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-area-wildlife-manager-wildlife-biologist-2-dillingham-alaska/4183885676</t>
+  </si>
+  <si>
+    <t>Campaign Associate for Non-profit</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location).</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campaign-associate-for-non-profit-boston-massachusetts/6634590564</t>
+  </si>
+  <si>
+    <t>Campus Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>The target annual compensation range for this position is $40,000 - $44,450 and depends on location, education and experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campus-organizer-chicago-illinois/4456509513</t>
+  </si>
+  <si>
+    <t>Community Outreach &amp; Environmental Educational Specialist 3</t>
+  </si>
+  <si>
+    <t>The Evergreen State College</t>
+  </si>
+  <si>
+    <t>Walla Walla, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$4,563 - $6,136 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-botany-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-community-outreach--environmental-educational-specialist-3-walla-walla-washington/4166613284</t>
+  </si>
+  <si>
+    <t>Conservation Advocate - Oceans</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>The starting annual compensation range for this position is $41,750-$46,000 for a candidate with 2-5 years of experience.</t>
+  </si>
+  <si>
+    <t>marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-advocate---oceans-washington-dc/5851220659</t>
+  </si>
+  <si>
+    <t>Conservation Director</t>
+  </si>
+  <si>
+    <t>Coastal Prairie Conservancy</t>
+  </si>
+  <si>
+    <t>Houston, TX</t>
+  </si>
+  <si>
+    <t>$60,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-director-houston-texas/6891084726</t>
+  </si>
+  <si>
+    <t>Conservation Engagement &amp; Learning Manager</t>
+  </si>
+  <si>
+    <t>Palm Beach Zoo &amp; Conservation Society</t>
+  </si>
+  <si>
+    <t>West Palm Beach, FL</t>
+  </si>
+  <si>
+    <t>A competitive salary, commensurate with your skills and experience.</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-engagement--learning-manager-west-palm-beach-florida/6614763851</t>
+  </si>
+  <si>
+    <t>Conservation Manager</t>
+  </si>
+  <si>
+    <t>Mississippi Valley Conservancy</t>
+  </si>
+  <si>
+    <t>La Crosse, WI</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-manager-la-crosse-wisconsin/4906224462</t>
+  </si>
+  <si>
+    <t>Consumer Advocacy Campaign Associate</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-consumer-advocacy-campaign-associate-washington-dc/8057432739</t>
+  </si>
+  <si>
+    <t>Crest Runner</t>
+  </si>
+  <si>
+    <t>Pacific Crest Trail Association</t>
+  </si>
+  <si>
+    <t>Southern, CA</t>
+  </si>
+  <si>
+    <t>$22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crest-runner-southern-california/2617238896</t>
+  </si>
+  <si>
+    <t>Data Management Specialist 1- Video Reader</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Red, CA</t>
+  </si>
+  <si>
+    <t>$19.58 - $28.38 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-data-management-specialist-1--video-reader-red-california/2506034876</t>
+  </si>
+  <si>
+    <t>Deputy Chief, Transportation, Infrastructure, and Construction - Program Manager VII - (260005U8)</t>
+  </si>
+  <si>
+    <t>Massachusetts Department of Conservation and Recreation</t>
+  </si>
+  <si>
+    <t>$102,855.80 - $158,640.55 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-chief-transportation-infrastructure-and-construction---program-manager-vii----260005u8-boston-massachusetts/5459475210</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Chikaming Open Lands</t>
+  </si>
+  <si>
+    <t>Sawyer, MI</t>
+  </si>
+  <si>
+    <t>$45,000 - $50,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-associate-sawyer-michigan/5336846982</t>
+  </si>
+  <si>
+    <t>End Food Waste Advocate</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>The starting compensation range for someone with 2-5 years of relevant professional experience is $41,750-$46,000.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-end-food-waste-advocate-portland-oregon/3791991185</t>
+  </si>
+  <si>
+    <t>Environmental Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Green Corps</t>
+  </si>
+  <si>
+    <t>Philadelphia, PA</t>
+  </si>
+  <si>
+    <t>For positions starting in August 2027, the target annual compensation is $41,000 (but compensation may range between $41,000 and $44,450 depending on location).</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaign-organizer-philadelphia-pennsylvania/2021664506</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaign-organizer-los-angeles-california/7341854456</t>
+  </si>
+  <si>
+    <t>Charlotte, NC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-campaign-organizer-charlotte-north-carolina/2838568602</t>
+  </si>
+  <si>
+    <t>Environmental Planning Program Manager</t>
+  </si>
+  <si>
+    <t>Coastal Bend Council of Governments</t>
+  </si>
+  <si>
+    <t>Corpus Christi, TX</t>
+  </si>
+  <si>
+    <t>$65,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-planning-program-manager-corpus-christi-texas/7576391379</t>
+  </si>
+  <si>
+    <t>Event &amp; Donor Relations Coordinator</t>
+  </si>
+  <si>
+    <t>Holden Forests &amp; Gardens</t>
+  </si>
+  <si>
+    <t>Cleveland, OH</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-event--donor-relations-coordinator-cleveland-ohio/5431616138</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Friends of Nevada Wilderness</t>
+  </si>
+  <si>
+    <t>Reno, NV</t>
+  </si>
+  <si>
+    <t>$100,000 - $115,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-reno-nevada/9972569969</t>
+  </si>
+  <si>
+    <t>Fisheries Populations Monitoring and Regulations Manager</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$93,542 - $134,592 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-populations-monitoring-and-regulations-manager-st-paul-minnesota/3570971236</t>
+  </si>
+  <si>
+    <t>Forestry Specialist Intermediate</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Big Falls, MN</t>
+  </si>
+  <si>
+    <t>$26.89 - $39.22 / hourly; $56,146 - $81,891 / annually</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-specialist-intermediate-big-falls-minnesota/2994161161</t>
+  </si>
+  <si>
+    <t>Effie, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-specialist-intermediate-effie-minnesota/1108937662</t>
+  </si>
+  <si>
+    <t>Forestry Technician I (FIA Internship)</t>
+  </si>
+  <si>
+    <t>South Carolina Forestry Commission</t>
+  </si>
+  <si>
+    <t>Columbia, SC</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$18.72 per hour</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-technician-i-fia-internship-columbia-south-carolina/4063607774</t>
+  </si>
+  <si>
+    <t>Forestry Technician I (State Forest Internship)</t>
+  </si>
+  <si>
+    <t>Multiple Locations, SC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-technician-i-state-forest-internship-multiple-locations-south-carolina/8512826814</t>
+  </si>
+  <si>
+    <t>Grants and Contracts Specialist</t>
+  </si>
+  <si>
+    <t>Maryland Coastal Bays Program</t>
+  </si>
+  <si>
+    <t>Berlin, MD</t>
+  </si>
+  <si>
+    <t>$57,000 - $62,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grants-and-contracts-specialist-berlin-maryland/4451615062</t>
+  </si>
+  <si>
+    <t>Leave &amp; Benefits Specialist</t>
+  </si>
+  <si>
+    <t>Kansas Department of Wildlife and Parks</t>
+  </si>
+  <si>
+    <t>Topeka, KS</t>
+  </si>
+  <si>
+    <t>$20.13 - $21.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-leave--benefits-specialist-topeka-kansas/9265266272</t>
+  </si>
+  <si>
+    <t>Logisitcs Coordinator</t>
+  </si>
+  <si>
+    <t>Kayak Adventuers Worldwide</t>
+  </si>
+  <si>
+    <t>Seward, AK</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-logisitcs-coordinator-seward-alaska/6198300203</t>
+  </si>
+  <si>
+    <t>Montana AgCorps Member</t>
+  </si>
+  <si>
+    <t>Montana AgCorps</t>
+  </si>
+  <si>
+    <t>Helena, MT</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$23,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-montana-agcorps-member-helena-montana/5199018859</t>
+  </si>
+  <si>
+    <t>Natural Resources Forestry Specialist Intermediate</t>
+  </si>
+  <si>
+    <t>Aitkin, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-forestry-specialist-intermediate-aitkin-minnesota/3471126731</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist I - II - III (Wildlife District 11 Biologist)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife Department</t>
+  </si>
+  <si>
+    <t>Kingsville, TX</t>
+  </si>
+  <si>
+    <t>$4,504.18 - $5,824.14 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-i---ii---iii-wildlife-district-11-biologist-kingsville-texas/2837200051</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist I - II - III (WMA Biologist)</t>
+  </si>
+  <si>
+    <t>Cotulla, TX</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-i---ii---iii-wma-biologist-cotulla-texas/9075780891</t>
+  </si>
+  <si>
+    <t>Natural Resources Specialist IV (Environmental Review Biologist)</t>
+  </si>
+  <si>
+    <t>Tyler, TX</t>
+  </si>
+  <si>
+    <t>$6,776.85 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-specialist-iv-environmental-review-biologist-tyler-texas/7476468174</t>
+  </si>
+  <si>
+    <t>Nature-Based Early Childhood Educator</t>
+  </si>
+  <si>
+    <t>Conchitas Outdoor Learning and Play</t>
+  </si>
+  <si>
+    <t>Mashpee, MA</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nature-based-early-childhood-educator-mashpee-massachusetts/1986033246</t>
+  </si>
+  <si>
+    <t>Outreach &amp; Programs Manager</t>
+  </si>
+  <si>
+    <t>The Alaska Center/Alaska Center Education Fund dba Trailside Discovery Camp</t>
+  </si>
+  <si>
+    <t>Anchorage, AK</t>
+  </si>
+  <si>
+    <t>$67 - $69 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outreach--programs-manager-anchorage-alaska/6655704145</t>
+  </si>
+  <si>
+    <t>Production Manager</t>
+  </si>
+  <si>
+    <t>Native Roots LLC</t>
+  </si>
+  <si>
+    <t>Twin Falls, ID</t>
+  </si>
+  <si>
+    <t>$65,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-production-manager-twin-falls-idaho/9895790757</t>
+  </si>
+  <si>
+    <t>Program Supervisor V (Nongame and Rare Species Program Leader)</t>
+  </si>
+  <si>
+    <t>TBD Statewide, TX</t>
+  </si>
+  <si>
+    <t>$7,694.42 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-supervisor-v-nongame-and-rare-species-program-leader-tbd-statewide-texas/9133871776</t>
+  </si>
+  <si>
+    <t>Restoration Project Manager</t>
+  </si>
+  <si>
+    <t>Sky Island Alliance</t>
+  </si>
+  <si>
+    <t>Tucson, AZ</t>
+  </si>
+  <si>
+    <t>$65,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-project-manager-tucson-arizona/9332364988</t>
+  </si>
+  <si>
+    <t>Scientific Aid</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Redding, CA</t>
+  </si>
+  <si>
+    <t>$18.26 - $21.67 per hour</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-scientific-aid-redding-california/2821836829</t>
+  </si>
+  <si>
+    <t>Sea Kayak Guide / Naturalist</t>
+  </si>
+  <si>
+    <t>Kayak Adventures Worldwide</t>
+  </si>
+  <si>
+    <t>$130 - $175 per day</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sea-kayak-guide--naturalist-seward-alaska/5946121284</t>
+  </si>
+  <si>
+    <t>Senior Conservation Project Manager</t>
+  </si>
+  <si>
+    <t>Upper Valley Land Trust</t>
+  </si>
+  <si>
+    <t>Hanover, NH</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-conservation-project-manager-hanover-new-hampshire/8690920638</t>
+  </si>
+  <si>
+    <t>Shooting Sports Recruitment Coordinator – Michigan</t>
+  </si>
+  <si>
+    <t>Council to Advance Hunting and the Shooting Sports/Michigan Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Lansing, Michigan area, with a hybrid working environment, MI</t>
+  </si>
+  <si>
+    <t>$55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-shooting-sports-recruitment-coordinator--michigan-lansing-michigan-area-with-a-hybrid-working-environment-michigan/4369081058</t>
+  </si>
+  <si>
+    <t>South Bay Section Leader</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>$11,437 - $14,315 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-south-bay-section-leader-oakland-california/3421918853</t>
+  </si>
+  <si>
+    <t>TPWD - Administrative Assistant V (Office Manager)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>Toyavale, TX</t>
+  </si>
+  <si>
+    <t>$4,769.07 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---administrative-assistant-v-office-manager-toyavale-texas/3532103296</t>
+  </si>
+  <si>
+    <t>USDA-ARS Plant Molecular Biology</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Albany, CA</t>
+  </si>
+  <si>
+    <t>Stipend $5,000.00 – $6,000.00 Monthly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-plant-molecular-biology-albany-california/6311967173</t>
+  </si>
+  <si>
+    <t>USGS Ecological Statistics Research and Development</t>
+  </si>
+  <si>
+    <t>U.S. Department of the Interior (DOI)</t>
+  </si>
+  <si>
+    <t>Bozeman, MT</t>
+  </si>
+  <si>
+    <t>Stipend $66,000.00 – $85,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usgs-ecological-statistics-research-and-development-bozeman-montana/2165688424</t>
+  </si>
+  <si>
+    <t>USGS The Use of Comprehensive Fish Health Assessments for Invasive Catfish in the Chesapeake Bay Drainage</t>
+  </si>
+  <si>
+    <t>Kearneysville, WV</t>
+  </si>
+  <si>
+    <t>Stipend $80,000.00 – $100,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usgs-the-use-of-comprehensive-fish-health-assessments-for-invasive-catfish-in-the-chesapeake-bay-drainage-kearneysville-west-virginia/7673113430</t>
+  </si>
+  <si>
+    <t>Volunteer &amp; Visitor Services Coordinator</t>
+  </si>
+  <si>
+    <t>Glen Helen Association</t>
+  </si>
+  <si>
+    <t>Yellow Springs, OH</t>
+  </si>
+  <si>
+    <t>$19.72 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-volunteer--visitor-services-coordinator-yellow-springs-ohio/6880445001</t>
+  </si>
+  <si>
+    <t>Water Quality Scientist (TMDL Planner)</t>
+  </si>
+  <si>
+    <t>Montana Department of Environmental Quality</t>
+  </si>
+  <si>
+    <t>$66,040 - $80,080 per year</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-quality-scientist-tmdl-planner-helena-montana/6518237045</t>
+  </si>
+  <si>
+    <t>Watershed Specialist</t>
+  </si>
+  <si>
+    <t>Pike County Conservation District</t>
+  </si>
+  <si>
+    <t>Hawley, PA</t>
+  </si>
+  <si>
+    <t>$50,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-specialist-hawley-pennsylvania/4243512070</t>
+  </si>
+  <si>
+    <t>Administrador(a) de Operaciones y Eventos</t>
+  </si>
+  <si>
+    <t>Salesianos de Don Bosco AC</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>MXN 18000.00 - 18000.00/month</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0f375ca68eb46bb906673a6dee2d78a-administradora-de-operaciones-y-eventos-salesianos-de-don-bosco-ac-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>Sage Compassion for Animals</t>
+  </si>
+  <si>
+    <t>Remote (San Francisco, California)</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/846cc28775b34807b8e236803528c04a-administrative-coordinator-sage-compassion-for-animals-san-francisco</t>
+  </si>
+  <si>
+    <t>Administrative Coordinator - Eviction Defense Center Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 52500.00 - 59055.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a1e1783ef4b4f0b83bec2fda4f6d770-administrative-coordinator-eviction-defense-center-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Advancement and Fundraising Associate (Part-Time)</t>
+  </si>
+  <si>
+    <t>Margaret Fuller Neighborhood House</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1997d83ec508446884ba6ce54895bb6c-advancement-and-fundraising-associate-part-time-margaret-fuller-neighborhood-house-cambridge</t>
+  </si>
+  <si>
+    <t>Assistant Director of Operations</t>
+  </si>
+  <si>
+    <t>Thompson Markward Hall</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 102000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e86c7c0b82af4404b32df39f6ce1a6fe-assistant-director-of-operations-thompson-markward-hall-washington</t>
+  </si>
+  <si>
+    <t>Associate Community Organizer</t>
+  </si>
+  <si>
+    <t>Direct Action &amp; Research Training Center</t>
+  </si>
+  <si>
+    <t>Tampa, Florida</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/930b56914af94f0281b839311a6d59fe-associate-community-organizer-direct-action-research-training-center-tampa</t>
+  </si>
+  <si>
+    <t>Columbus, Ohio</t>
+  </si>
+  <si>
+    <t>USD 52000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4a881cda6b444a9a52ddcd780f48fd5-associate-community-organizer-direct-action-research-training-center-columbus</t>
+  </si>
+  <si>
+    <t>Wichita, Kansas</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23c18f946b82458c964a90fd7ea9be80-associate-community-organizer-direct-action-research-training-center-wichita</t>
+  </si>
+  <si>
+    <t>Chief Advancement Officer</t>
+  </si>
+  <si>
+    <t>Friends of the Children - SF Bay Area</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7515e30bce35483e8c83d189577c069d-chief-advancement-officer-friends-of-the-children-sf-bay-area-san-francisco</t>
+  </si>
+  <si>
+    <t>Church Partner &amp; Outpost Director</t>
+  </si>
+  <si>
+    <t>Uncharted International Inc</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed4d6ccdb60c415683e135567868cd66-church-partner-outpost-director-uncharted-international-inc-denver</t>
+  </si>
+  <si>
+    <t>Communications and Media Relations Manager for World BEYOND War</t>
+  </si>
+  <si>
+    <t>World BEYOND War</t>
+  </si>
+  <si>
+    <t>USD 1000.00 - 2500.00/month</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2c7703cb1644ae9b67c85db7569eaaa-communications-and-media-relations-manager-for-world-beyond-war-world-beyond-war-charlottesville</t>
+  </si>
+  <si>
+    <t>Community Engagement and Events Coordinator</t>
+  </si>
+  <si>
+    <t>Nova Institute for Health</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Research Social Science, Health Medicine, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e2fe4e08d1d4adda2b9bf0e8ec9cafc-community-engagement-and-events-coordinator-nova-institute-for-health-baltimore</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>Northwest Indian Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Olympia, Washington</t>
+  </si>
+  <si>
+    <t>USD 112430.00 - 167532.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c0829b11328948b3aa3d2dcb736fbdad-controller-northwest-indian-fisheries-commission-olympia</t>
+  </si>
+  <si>
+    <t>Culinary Operation Manager</t>
+  </si>
+  <si>
+    <t>Holy Apostles Soup Kitchen</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92f013a974964207ba22b94d3c4e9d66-culinary-operation-manager-holy-apostles-soup-kitchen-new-york</t>
+  </si>
+  <si>
+    <t>Deputy Campaign Director</t>
+  </si>
+  <si>
+    <t>Design It For Us</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d627146cad4e424688a30f9ee6fab226-deputy-campaign-director-design-it-for-us-washington</t>
+  </si>
+  <si>
+    <t>Director - U.S. Operations</t>
+  </si>
+  <si>
+    <t>Make a Miracle Corp</t>
+  </si>
+  <si>
+    <t>Alpharetta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Disaster Relief</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/35472ecd80714a19b7627eb2918f3ad9-director-us-operations-make-a-miracle-corp-alpharetta</t>
+  </si>
+  <si>
+    <t>Director of Communications &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Ivymount Organization</t>
+  </si>
+  <si>
+    <t>Potomac, Maryland</t>
+  </si>
+  <si>
+    <t>USD 120000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b2df2af63d84097b304a80b5d7663bf-director-of-communications-marketing-ivymount-organization-potomac</t>
+  </si>
+  <si>
+    <t>Director of Community Initiatives &amp; Services</t>
+  </si>
+  <si>
+    <t>Educational Alliance</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/871dc5c2f53f4d87939ba3e434a47bda-director-of-community-initiatives-services-educational-alliance-new-york</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Denver Public Schools Foundation</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6673c6ae9ab4d9584fec64b1c98d664-director-of-finance-denver-public-schools-foundation-denver</t>
+  </si>
+  <si>
+    <t>Director of Legal Services</t>
+  </si>
+  <si>
+    <t>Levitt &amp; Quinn Family Law Center, Inc.</t>
+  </si>
+  <si>
+    <t>USD 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f0466313ec1a4a1ba408efff5bb98e45-director-of-legal-services-levitt-quinn-family-law-center-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>Director of Organizing</t>
+  </si>
+  <si>
+    <t>Roanoke, Virginia</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8225ae4d1bb54623b22fec2254ada67c-director-of-organizing-direct-action-research-training-center-roanoke</t>
+  </si>
+  <si>
+    <t>Fort Myers, Florida</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75c30554da904ac882cc3ecb292ebe95-director-of-organizing-direct-action-research-training-center-fort-myers</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18e8ec379ee94e86af0e168b7e2c700e-director-of-organizing-direct-action-research-training-center-richmond</t>
+  </si>
+  <si>
+    <t>Events &amp; Outreach Manager</t>
+  </si>
+  <si>
+    <t>Piedmont Environmental Alliance</t>
+  </si>
+  <si>
+    <t>Winston-Salem, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 48000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14092c271bba44a98e142835c9dd1a55-events-outreach-manager-piedmont-environmental-alliance-winston-salem</t>
+  </si>
+  <si>
+    <t>Farm Business Advisor</t>
+  </si>
+  <si>
+    <t>Kitchen Table Advisors</t>
+  </si>
+  <si>
+    <t>Napa, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Economic Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5291e3a7611343baa5f81f7a490d3eba-farm-business-advisor-kitchen-table-advisors-napa</t>
+  </si>
+  <si>
+    <t>Grants and Finance Manager</t>
+  </si>
+  <si>
+    <t>BERGSTROM FOUNDATION</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Women, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9bd44e6c60824cbaa6b0928e7db25a01-grants-and-finance-manager-bergstrom-foundation-berkeley</t>
+  </si>
+  <si>
+    <t>House Manager/Founding House Leader</t>
+  </si>
+  <si>
+    <t>L'Arche Southern Vermont</t>
+  </si>
+  <si>
+    <t>Brattleboro, Vermont</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60b9ac1a527d4d03a5733957612915f9-house-managerfounding-house-leader-larche-southern-vermont-brattleboro</t>
+  </si>
+  <si>
+    <t>Immigrant Defense Lead Organizer</t>
+  </si>
+  <si>
+    <t>Street Level Health Project</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f30209328bd74151bf2c1d5e8b27d5bb-immigrant-defense-lead-organizer-street-level-health-project-oakland</t>
+  </si>
+  <si>
+    <t>Immigrant Defense Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02e69bf68337499ab1f00c8de6c90599-immigrant-defense-outreach-coordinator-street-level-health-project-oakland</t>
+  </si>
+  <si>
+    <t>Manager of Financial Planning &amp; Analysis (FP &amp; A)</t>
+  </si>
+  <si>
+    <t>1199 SEIU United Healthcare Workers East</t>
+  </si>
+  <si>
+    <t>USD 149999.00 - 156000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d4e0fe6b3d6463a9a49fd18ef14aeeb-manager-of-financial-planning-analysis-fp-a-1199-seiu-united-healthcare-workers-east-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Education &amp; Workforce Pathways</t>
+  </si>
+  <si>
+    <t>United Way of New York City</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96782a81f0224221aaf77f08da2320bf-manager-education-workforce-pathways-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Managing Director, Entertainment</t>
+  </si>
+  <si>
+    <t>Resetting the Table</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c9baa53d32248758a14481ebe30b31b-managing-director-entertainment-resetting-the-table-el-cerrito</t>
+  </si>
+  <si>
+    <t>Mitigation Advancement Program Staff Attorney</t>
+  </si>
+  <si>
+    <t>Capital Area Private Defender Service Post-Conviction Division</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9de061650901476fa98e945f1012e46b-mitigation-advancement-program-staff-attorney-capital-area-private-defender-service-post-conviction-division-austin</t>
+  </si>
+  <si>
+    <t>Non-Capital Training Attorney</t>
+  </si>
+  <si>
+    <t>Office of the State Public Defender (OSPD)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 11993.00 - 16096.00/month</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/a81ffb4f18b74eaaa6f22a3889cd5932-non-capital-training-attorney-office-of-the-state-public-defender-ospd-oakland</t>
+  </si>
+  <si>
+    <t>NW Chief Engineer</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 98000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f157298a86244909208bd4627755057-nw-chief-engineer-opb-portland</t>
+  </si>
+  <si>
+    <t>Operations and Events Coordinator</t>
+  </si>
+  <si>
+    <t>The Washington Ballet</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d134e336958547c291a85d96de24f91c-operations-and-events-coordinator-the-washington-ballet-washington</t>
+  </si>
+  <si>
+    <t>Popular Education Coordinator</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7bcfcc6a48d74852867c039a1b7c95a0-popular-education-coordinator-street-level-health-project-oakland</t>
+  </si>
+  <si>
+    <t>Post-Conviction Staff Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f6d6f647c2c452ca6feccca31357bb2-post-conviction-staff-attorney-capital-area-private-defender-service-post-conviction-division-austin</t>
+  </si>
+  <si>
+    <t>Program Officer – Participant and Alumni Engagement, J. Christopher Stevens Digital Leaders Program</t>
+  </si>
+  <si>
+    <t>American Councils for International Education: ACTR/ACCELS</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a40fc4f871442dcbd0e65c4ab9cbac1-program-officer-participant-and-alumni-engagement-j-christopher-stevens-digital-leaders-program-american-councils-for-international-education-actraccels-washington</t>
+  </si>
+  <si>
+    <t>Program Officer – Selection and Administration J. Christopher Stevens Digital Leaders Program</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/730f03b308a34aafbbdb692ceb4487d1-program-officer-selection-and-administration-j-christopher-stevens-digital-leaders-program-american-councils-for-international-education-actraccels-washington</t>
+  </si>
+  <si>
+    <t>Regional Field Manager, Environmental Services (Job #372) ($111,419 - $122,945)</t>
+  </si>
+  <si>
+    <t>Rural Community Assistance Corporation (RCAC)</t>
+  </si>
+  <si>
+    <t>West Sacramento, California</t>
+  </si>
+  <si>
+    <t>USD 111419.00 - 122945.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c5f4770e34ad471689827722d6db6127-regional-field-manager-environmental-services-job-372-111419-122945-rural-community-assistance-corporation-rcac-west-sacramento</t>
+  </si>
+  <si>
+    <t>Senior Accountant (Temporary)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/124961e1cfa442098570f2c4ac7a6e75-senior-accountant-temporary-united-way-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Strings and Orchestra Program Director</t>
+  </si>
+  <si>
+    <t>Merit School of Music</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/771e9502ffcb4892b7fafee1661f320b-strings-and-orchestra-program-director-merit-school-of-music-chicago</t>
+  </si>
+  <si>
+    <t>Volunteer &amp; Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Bikes for the World</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/23675146769e46bba69c6228e3370866-volunteer-outreach-coordinator-bikes-for-the-world-rockville</t>
+  </si>
+  <si>
+    <t>Volunteer Coordinator</t>
+  </si>
+  <si>
+    <t>Mitzvah Circle</t>
+  </si>
+  <si>
+    <t>Lansdale, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 43000.00 - 43000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d43520ed4b7144e797f05a134dd1a311-volunteer-coordinator-mitzvah-circle-lansdale</t>
+  </si>
+  <si>
+    <t>Washington Director of External Engagement</t>
+  </si>
+  <si>
+    <t>Israel Policy Forum</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>International Relations, International Relations, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f991b7ec643a4d059f46ab307be5cd1d-washington-director-of-external-engagement-israel-policy-forum-washington</t>
+  </si>
+  <si>
+    <t>Washington Legislative Director</t>
+  </si>
+  <si>
+    <t>Climate Solutions</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a8b533efd6fb4d13a9599a6847dd3b68-washington-legislative-director-climate-solutions-los-angeles</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1530,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1556,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +1899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +1938,1210 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F28" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" t="s">
+        <v>149</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" t="s">
+        <v>105</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" t="s">
+        <v>123</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>161</v>
+      </c>
+      <c r="B32" t="s">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s">
+        <v>163</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>166</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>164</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" t="s">
+        <v>174</v>
+      </c>
+      <c r="C35" t="s">
+        <v>175</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" t="s">
+        <v>179</v>
+      </c>
+      <c r="C36" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>181</v>
+      </c>
+      <c r="F36" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>184</v>
+      </c>
+      <c r="B37" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" t="s">
+        <v>186</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" t="s">
+        <v>188</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>193</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>197</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>198</v>
+      </c>
+      <c r="F39" t="s">
+        <v>199</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>204</v>
+      </c>
+      <c r="F40" t="s">
+        <v>205</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>207</v>
+      </c>
+      <c r="B41" t="s">
+        <v>208</v>
+      </c>
+      <c r="C41" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>214</v>
+      </c>
+      <c r="F42" t="s">
+        <v>42</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>216</v>
+      </c>
+      <c r="B43" t="s">
+        <v>217</v>
+      </c>
+      <c r="C43" t="s">
+        <v>218</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>219</v>
+      </c>
+      <c r="F43" t="s">
+        <v>220</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>222</v>
+      </c>
+      <c r="B44" t="s">
+        <v>202</v>
+      </c>
+      <c r="C44" t="s">
+        <v>223</v>
+      </c>
+      <c r="D44" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" t="s">
+        <v>224</v>
+      </c>
+      <c r="F44" t="s">
+        <v>205</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" t="s">
+        <v>227</v>
+      </c>
+      <c r="C45" t="s">
+        <v>228</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>229</v>
+      </c>
+      <c r="F45" t="s">
+        <v>105</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>231</v>
+      </c>
+      <c r="B46" t="s">
+        <v>232</v>
+      </c>
+      <c r="C46" t="s">
+        <v>233</v>
+      </c>
+      <c r="D46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E46" t="s">
+        <v>234</v>
+      </c>
+      <c r="F46" t="s">
+        <v>188</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" t="s">
+        <v>238</v>
+      </c>
+      <c r="D47" t="s">
+        <v>130</v>
+      </c>
+      <c r="E47" t="s">
+        <v>239</v>
+      </c>
+      <c r="F47" t="s">
+        <v>240</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>242</v>
+      </c>
+      <c r="B48" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" t="s">
+        <v>243</v>
+      </c>
+      <c r="D48" t="s">
+        <v>130</v>
+      </c>
+      <c r="E48" t="s">
+        <v>244</v>
+      </c>
+      <c r="F48" t="s">
+        <v>245</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>247</v>
+      </c>
+      <c r="B49" t="s">
+        <v>248</v>
+      </c>
+      <c r="C49" t="s">
+        <v>249</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>250</v>
+      </c>
+      <c r="F49" t="s">
+        <v>220</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>252</v>
+      </c>
+      <c r="B50" t="s">
+        <v>253</v>
+      </c>
+      <c r="C50" t="s">
+        <v>154</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>254</v>
+      </c>
+      <c r="F50" t="s">
+        <v>255</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>260</v>
+      </c>
+      <c r="F51" t="s">
+        <v>261</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3197,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3236,1138 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F4" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>282</v>
+      </c>
+      <c r="B5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" t="s">
+        <v>287</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F6" t="s">
+        <v>293</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F7" t="s">
+        <v>298</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" t="s">
+        <v>301</v>
+      </c>
+      <c r="F8" t="s">
+        <v>302</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" t="s">
+        <v>305</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" t="s">
+        <v>310</v>
+      </c>
+      <c r="F10" t="s">
+        <v>311</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" t="s">
+        <v>266</v>
+      </c>
+      <c r="E11" t="s">
+        <v>298</v>
+      </c>
+      <c r="F11" t="s">
+        <v>316</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>318</v>
+      </c>
+      <c r="B12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" t="s">
+        <v>315</v>
+      </c>
+      <c r="D12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F12" t="s">
+        <v>321</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>323</v>
+      </c>
+      <c r="B13" t="s">
+        <v>324</v>
+      </c>
+      <c r="C13" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" t="s">
+        <v>326</v>
+      </c>
+      <c r="E13" t="s">
+        <v>327</v>
+      </c>
+      <c r="F13" t="s">
+        <v>328</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>330</v>
+      </c>
+      <c r="B14" t="s">
+        <v>331</v>
+      </c>
+      <c r="C14" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" t="s">
+        <v>266</v>
+      </c>
+      <c r="E14" t="s">
+        <v>333</v>
+      </c>
+      <c r="F14" t="s">
+        <v>334</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B15" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" t="s">
+        <v>338</v>
+      </c>
+      <c r="D15" t="s">
+        <v>266</v>
+      </c>
+      <c r="E15" t="s">
+        <v>339</v>
+      </c>
+      <c r="F15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E16" t="s">
+        <v>344</v>
+      </c>
+      <c r="F16" t="s">
+        <v>345</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>347</v>
+      </c>
+      <c r="B17" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" t="s">
+        <v>349</v>
+      </c>
+      <c r="D17" t="s">
+        <v>266</v>
+      </c>
+      <c r="E17" t="s">
+        <v>350</v>
+      </c>
+      <c r="F17" t="s">
+        <v>351</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" t="s">
+        <v>354</v>
+      </c>
+      <c r="C18" t="s">
+        <v>355</v>
+      </c>
+      <c r="D18" t="s">
+        <v>266</v>
+      </c>
+      <c r="E18" t="s">
+        <v>356</v>
+      </c>
+      <c r="F18" t="s">
+        <v>357</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>359</v>
+      </c>
+      <c r="B19" t="s">
+        <v>360</v>
+      </c>
+      <c r="C19" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" t="s">
+        <v>266</v>
+      </c>
+      <c r="E19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F19" t="s">
+        <v>362</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>364</v>
+      </c>
+      <c r="B20" t="s">
+        <v>365</v>
+      </c>
+      <c r="C20" t="s">
+        <v>366</v>
+      </c>
+      <c r="D20" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" t="s">
+        <v>367</v>
+      </c>
+      <c r="F20" t="s">
+        <v>368</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>370</v>
+      </c>
+      <c r="B21" t="s">
+        <v>371</v>
+      </c>
+      <c r="C21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" t="s">
+        <v>266</v>
+      </c>
+      <c r="E21" t="s">
+        <v>372</v>
+      </c>
+      <c r="F21" t="s">
+        <v>373</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>375</v>
+      </c>
+      <c r="B22" t="s">
+        <v>296</v>
+      </c>
+      <c r="C22" t="s">
+        <v>376</v>
+      </c>
+      <c r="D22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E22" t="s">
+        <v>377</v>
+      </c>
+      <c r="F22" t="s">
+        <v>378</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C23" t="s">
+        <v>380</v>
+      </c>
+      <c r="D23" t="s">
+        <v>266</v>
+      </c>
+      <c r="E23" t="s">
+        <v>381</v>
+      </c>
+      <c r="F23" t="s">
+        <v>378</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B24" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" t="s">
+        <v>383</v>
+      </c>
+      <c r="D24" t="s">
+        <v>266</v>
+      </c>
+      <c r="E24" t="s">
+        <v>384</v>
+      </c>
+      <c r="F24" t="s">
+        <v>378</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>386</v>
+      </c>
+      <c r="B25" t="s">
+        <v>387</v>
+      </c>
+      <c r="C25" t="s">
+        <v>388</v>
+      </c>
+      <c r="D25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" t="s">
+        <v>389</v>
+      </c>
+      <c r="F25" t="s">
+        <v>390</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>392</v>
+      </c>
+      <c r="B26" t="s">
+        <v>393</v>
+      </c>
+      <c r="C26" t="s">
+        <v>394</v>
+      </c>
+      <c r="D26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" t="s">
+        <v>395</v>
+      </c>
+      <c r="F26" t="s">
+        <v>396</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>398</v>
+      </c>
+      <c r="B27" t="s">
+        <v>399</v>
+      </c>
+      <c r="C27" t="s">
+        <v>400</v>
+      </c>
+      <c r="D27" t="s">
+        <v>266</v>
+      </c>
+      <c r="E27" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27" t="s">
+        <v>402</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>404</v>
+      </c>
+      <c r="B28" t="s">
+        <v>405</v>
+      </c>
+      <c r="C28" t="s">
+        <v>406</v>
+      </c>
+      <c r="D28" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" t="s">
+        <v>407</v>
+      </c>
+      <c r="F28" t="s">
+        <v>408</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>410</v>
+      </c>
+      <c r="B29" t="s">
+        <v>411</v>
+      </c>
+      <c r="C29" t="s">
+        <v>412</v>
+      </c>
+      <c r="D29" t="s">
+        <v>266</v>
+      </c>
+      <c r="E29" t="s">
+        <v>413</v>
+      </c>
+      <c r="F29" t="s">
+        <v>414</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>416</v>
+      </c>
+      <c r="B30" t="s">
+        <v>411</v>
+      </c>
+      <c r="C30" t="s">
+        <v>412</v>
+      </c>
+      <c r="D30" t="s">
+        <v>266</v>
+      </c>
+      <c r="E30" t="s">
+        <v>417</v>
+      </c>
+      <c r="F30" t="s">
+        <v>414</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>419</v>
+      </c>
+      <c r="B31" t="s">
+        <v>420</v>
+      </c>
+      <c r="C31" t="s">
+        <v>338</v>
+      </c>
+      <c r="D31" t="s">
+        <v>266</v>
+      </c>
+      <c r="E31" t="s">
+        <v>421</v>
+      </c>
+      <c r="F31" t="s">
+        <v>422</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>424</v>
+      </c>
+      <c r="B32" t="s">
+        <v>425</v>
+      </c>
+      <c r="C32" t="s">
+        <v>338</v>
+      </c>
+      <c r="D32" t="s">
+        <v>266</v>
+      </c>
+      <c r="E32" t="s">
+        <v>298</v>
+      </c>
+      <c r="F32" t="s">
+        <v>298</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>427</v>
+      </c>
+      <c r="B33" t="s">
+        <v>428</v>
+      </c>
+      <c r="C33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D33" t="s">
+        <v>266</v>
+      </c>
+      <c r="E33" t="s">
+        <v>429</v>
+      </c>
+      <c r="F33" t="s">
+        <v>430</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>432</v>
+      </c>
+      <c r="B34" t="s">
+        <v>433</v>
+      </c>
+      <c r="C34" t="s">
+        <v>434</v>
+      </c>
+      <c r="D34" t="s">
+        <v>266</v>
+      </c>
+      <c r="E34" t="s">
+        <v>435</v>
+      </c>
+      <c r="F34" t="s">
+        <v>436</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>438</v>
+      </c>
+      <c r="B35" t="s">
+        <v>439</v>
+      </c>
+      <c r="C35" t="s">
+        <v>440</v>
+      </c>
+      <c r="D35" t="s">
+        <v>266</v>
+      </c>
+      <c r="E35" t="s">
+        <v>441</v>
+      </c>
+      <c r="F35" t="s">
+        <v>442</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>444</v>
+      </c>
+      <c r="B36" t="s">
+        <v>445</v>
+      </c>
+      <c r="C36" t="s">
+        <v>446</v>
+      </c>
+      <c r="D36" t="s">
+        <v>266</v>
+      </c>
+      <c r="E36" t="s">
+        <v>447</v>
+      </c>
+      <c r="F36" t="s">
+        <v>448</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>450</v>
+      </c>
+      <c r="B37" t="s">
+        <v>451</v>
+      </c>
+      <c r="C37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D37" t="s">
+        <v>266</v>
+      </c>
+      <c r="E37" t="s">
+        <v>452</v>
+      </c>
+      <c r="F37" t="s">
+        <v>298</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>454</v>
+      </c>
+      <c r="B38" t="s">
+        <v>411</v>
+      </c>
+      <c r="C38" t="s">
+        <v>412</v>
+      </c>
+      <c r="D38" t="s">
+        <v>266</v>
+      </c>
+      <c r="E38" t="s">
+        <v>417</v>
+      </c>
+      <c r="F38" t="s">
+        <v>455</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>457</v>
+      </c>
+      <c r="B39" t="s">
+        <v>433</v>
+      </c>
+      <c r="C39" t="s">
+        <v>434</v>
+      </c>
+      <c r="D39" t="s">
+        <v>266</v>
+      </c>
+      <c r="E39" t="s">
+        <v>298</v>
+      </c>
+      <c r="F39" t="s">
+        <v>436</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>459</v>
+      </c>
+      <c r="B40" t="s">
+        <v>460</v>
+      </c>
+      <c r="C40" t="s">
+        <v>291</v>
+      </c>
+      <c r="D40" t="s">
+        <v>266</v>
+      </c>
+      <c r="E40" t="s">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>298</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>463</v>
+      </c>
+      <c r="B41" t="s">
+        <v>460</v>
+      </c>
+      <c r="C41" t="s">
+        <v>291</v>
+      </c>
+      <c r="D41" t="s">
+        <v>266</v>
+      </c>
+      <c r="E41" t="s">
+        <v>461</v>
+      </c>
+      <c r="F41" t="s">
+        <v>298</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>465</v>
+      </c>
+      <c r="B42" t="s">
+        <v>466</v>
+      </c>
+      <c r="C42" t="s">
+        <v>467</v>
+      </c>
+      <c r="D42" t="s">
+        <v>266</v>
+      </c>
+      <c r="E42" t="s">
+        <v>468</v>
+      </c>
+      <c r="F42" t="s">
+        <v>298</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>470</v>
+      </c>
+      <c r="B43" t="s">
+        <v>425</v>
+      </c>
+      <c r="C43" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" t="s">
+        <v>471</v>
+      </c>
+      <c r="E43" t="s">
+        <v>472</v>
+      </c>
+      <c r="F43" t="s">
+        <v>298</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>474</v>
+      </c>
+      <c r="B44" t="s">
+        <v>475</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" t="s">
+        <v>413</v>
+      </c>
+      <c r="F44" t="s">
+        <v>476</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>478</v>
+      </c>
+      <c r="B45" t="s">
+        <v>479</v>
+      </c>
+      <c r="C45" t="s">
+        <v>480</v>
+      </c>
+      <c r="D45" t="s">
+        <v>266</v>
+      </c>
+      <c r="E45" t="s">
+        <v>481</v>
+      </c>
+      <c r="F45" t="s">
+        <v>482</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>484</v>
+      </c>
+      <c r="B46" t="s">
+        <v>485</v>
+      </c>
+      <c r="C46" t="s">
+        <v>486</v>
+      </c>
+      <c r="D46" t="s">
+        <v>266</v>
+      </c>
+      <c r="E46" t="s">
+        <v>487</v>
+      </c>
+      <c r="F46" t="s">
+        <v>488</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>490</v>
+      </c>
+      <c r="B47" t="s">
+        <v>491</v>
+      </c>
+      <c r="C47" t="s">
+        <v>291</v>
+      </c>
+      <c r="D47" t="s">
+        <v>266</v>
+      </c>
+      <c r="E47" t="s">
+        <v>492</v>
+      </c>
+      <c r="F47" t="s">
+        <v>493</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>495</v>
+      </c>
+      <c r="B48" t="s">
+        <v>496</v>
+      </c>
+      <c r="C48" t="s">
+        <v>278</v>
+      </c>
+      <c r="D48" t="s">
+        <v>266</v>
+      </c>
+      <c r="E48" t="s">
+        <v>497</v>
+      </c>
+      <c r="F48" t="s">
+        <v>498</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-12.xlsx
+++ b/docs/xlsx/jobs-2026-10-12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="541">
   <si>
     <t>Title</t>
   </si>
@@ -1108,6 +1108,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/871dc5c2f53f4d87939ba3e434a47bda-director-of-community-initiatives-services-educational-alliance-new-york</t>
   </si>
   <si>
+    <t>Director of Education</t>
+  </si>
+  <si>
+    <t>Foodwise</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/981ebecf6a1b4de99f48f40282d0d983-director-of-education-foodwise-san-francisco</t>
+  </si>
+  <si>
     <t>Director of Finance</t>
   </si>
   <si>
@@ -1174,6 +1189,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/18e8ec379ee94e86af0e168b7e2c700e-director-of-organizing-direct-action-research-training-center-richmond</t>
   </si>
   <si>
+    <t>Equitable Building Decarbonization Program Advisor</t>
+  </si>
+  <si>
+    <t>Climate Action Campaign</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 55120.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4a2568b7491c46ffb2510963dcf50c59-equitable-building-decarbonization-program-advisor-climate-action-campaign-santa-ana</t>
+  </si>
+  <si>
     <t>Events &amp; Outreach Manager</t>
   </si>
   <si>
@@ -1192,6 +1228,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/14092c271bba44a98e142835c9dd1a55-events-outreach-manager-piedmont-environmental-alliance-winston-salem</t>
   </si>
   <si>
+    <t>SUSTAINABLE SARATOGA</t>
+  </si>
+  <si>
+    <t>Saratoga Springs, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/395fa012715d4cebaee5901dcd7a3fc3-executive-director-sustainable-saratoga-saratoga-springs</t>
+  </si>
+  <si>
+    <t>Executive Director of SFWA</t>
+  </si>
+  <si>
+    <t>Science Fiction and Fantasy Writers Association</t>
+  </si>
+  <si>
+    <t>USD 77000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a04a59f896e94bbaa1c6124d548d2c36-executive-director-of-sfwa-science-fiction-and-fantasy-writers-association-san-francisco</t>
+  </si>
+  <si>
     <t>Farm Business Advisor</t>
   </si>
   <si>
@@ -1210,6 +1276,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/5291e3a7611343baa5f81f7a490d3eba-farm-business-advisor-kitchen-table-advisors-napa</t>
   </si>
   <si>
+    <t>Food Pantry Financial Assistant</t>
+  </si>
+  <si>
+    <t>North Kingstown Food Pantry</t>
+  </si>
+  <si>
+    <t>North Kingstown, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Hunger Food Security, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e213b18b771a4d6ba3b579a9b869e3b7-food-pantry-financial-assistant-north-kingstown-food-pantry-north-kingstown</t>
+  </si>
+  <si>
     <t>Grants and Finance Manager</t>
   </si>
   <si>
@@ -1378,6 +1462,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d134e336958547c291a85d96de24f91c-operations-and-events-coordinator-the-washington-ballet-washington</t>
   </si>
   <si>
+    <t>ORGANIZING DIRECTOR</t>
+  </si>
+  <si>
+    <t>Sacred Heart Community Service</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0267396695a24922b74e0058c2e7df84-organizing-director-sacred-heart-community-service-san-jose</t>
+  </si>
+  <si>
     <t>Popular Education Coordinator</t>
   </si>
   <si>
@@ -1429,9 +1531,6 @@
     <t>Senior Accountant (Temporary)</t>
   </si>
   <si>
-    <t>Full Time, Temporary</t>
-  </si>
-  <si>
     <t>USD 78000.00 - 90000.00/year</t>
   </si>
   <si>
@@ -1450,6 +1549,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/771e9502ffcb4892b7fafee1661f320b-strings-and-orchestra-program-director-merit-school-of-music-chicago</t>
   </si>
   <si>
+    <t>Vice President of Development</t>
+  </si>
+  <si>
+    <t>Girls on the Run International</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b754c2accc3b4b309270ec7c8e780878-vice-president-of-development-girls-on-the-run-international-charlotte</t>
+  </si>
+  <si>
     <t>Volunteer &amp; Outreach Coordinator</t>
   </si>
   <si>
@@ -1514,6 +1628,15 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/a8b533efd6fb4d13a9599a6847dd3b68-washington-legislative-director-climate-solutions-los-angeles</t>
+  </si>
+  <si>
+    <t>West Coast Regional Engagement Director</t>
+  </si>
+  <si>
+    <t>Council on Foreign Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c334012541b442fab0a770a96c7ac88e-west-coast-regional-engagement-director-council-on-foreign-relations-new-york</t>
   </si>
 </sst>
 </file>
@@ -3197,7 +3320,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3658,30 +3781,30 @@
         <v>365</v>
       </c>
       <c r="C20" t="s">
+        <v>309</v>
+      </c>
+      <c r="D20" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" t="s">
         <v>366</v>
       </c>
-      <c r="D20" t="s">
-        <v>266</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>367</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>369</v>
+      </c>
+      <c r="B21" t="s">
         <v>370</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>371</v>
-      </c>
-      <c r="C21" t="s">
-        <v>278</v>
       </c>
       <c r="D21" t="s">
         <v>266</v>
@@ -3701,10 +3824,10 @@
         <v>375</v>
       </c>
       <c r="B22" t="s">
-        <v>296</v>
+        <v>376</v>
       </c>
       <c r="C22" t="s">
-        <v>376</v>
+        <v>278</v>
       </c>
       <c r="D22" t="s">
         <v>266</v>
@@ -3721,56 +3844,56 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B23" t="s">
         <v>296</v>
       </c>
       <c r="C23" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D23" t="s">
         <v>266</v>
       </c>
       <c r="E23" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F23" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B24" t="s">
         <v>296</v>
       </c>
       <c r="C24" t="s">
+        <v>385</v>
+      </c>
+      <c r="D24" t="s">
+        <v>266</v>
+      </c>
+      <c r="E24" t="s">
+        <v>386</v>
+      </c>
+      <c r="F24" t="s">
         <v>383</v>
       </c>
-      <c r="D24" t="s">
-        <v>266</v>
-      </c>
-      <c r="E24" t="s">
-        <v>384</v>
-      </c>
-      <c r="F24" t="s">
-        <v>378</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B25" t="s">
-        <v>387</v>
+        <v>296</v>
       </c>
       <c r="C25" t="s">
         <v>388</v>
@@ -3782,24 +3905,24 @@
         <v>389</v>
       </c>
       <c r="F25" t="s">
+        <v>383</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>391</v>
+      </c>
+      <c r="B26" t="s">
         <v>392</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>393</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>394</v>
-      </c>
-      <c r="D26" t="s">
-        <v>266</v>
       </c>
       <c r="E26" t="s">
         <v>395</v>
@@ -3836,59 +3959,59 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" t="s">
         <v>404</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>405</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>266</v>
+      </c>
+      <c r="E28" t="s">
         <v>406</v>
       </c>
-      <c r="D28" t="s">
-        <v>266</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>407</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>409</v>
+      </c>
+      <c r="B29" t="s">
         <v>410</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>315</v>
+      </c>
+      <c r="D29" t="s">
+        <v>266</v>
+      </c>
+      <c r="E29" t="s">
         <v>411</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" t="s">
         <v>412</v>
       </c>
-      <c r="D29" t="s">
-        <v>266</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="H29" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="F29" t="s">
-        <v>414</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>414</v>
+      </c>
+      <c r="B30" t="s">
+        <v>415</v>
+      </c>
+      <c r="C30" t="s">
         <v>416</v>
-      </c>
-      <c r="B30" t="s">
-        <v>411</v>
-      </c>
-      <c r="C30" t="s">
-        <v>412</v>
       </c>
       <c r="D30" t="s">
         <v>266</v>
@@ -3897,107 +4020,107 @@
         <v>417</v>
       </c>
       <c r="F30" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B31" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C31" t="s">
-        <v>338</v>
+        <v>422</v>
       </c>
       <c r="D31" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E31" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F31" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B32" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C32" t="s">
-        <v>338</v>
+        <v>428</v>
       </c>
       <c r="D32" t="s">
         <v>266</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>429</v>
       </c>
       <c r="F32" t="s">
-        <v>298</v>
+        <v>430</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="B33" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C33" t="s">
-        <v>315</v>
+        <v>434</v>
       </c>
       <c r="D33" t="s">
         <v>266</v>
       </c>
       <c r="E33" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F33" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B34" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C34" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D34" t="s">
         <v>266</v>
       </c>
       <c r="E34" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="F34" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B35" t="s">
         <v>439</v>
@@ -4009,274 +4132,274 @@
         <v>266</v>
       </c>
       <c r="E35" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F35" t="s">
         <v>442</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B36" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C36" t="s">
-        <v>446</v>
+        <v>338</v>
       </c>
       <c r="D36" t="s">
         <v>266</v>
       </c>
       <c r="E36" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F36" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B37" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C37" t="s">
-        <v>291</v>
+        <v>338</v>
       </c>
       <c r="D37" t="s">
         <v>266</v>
       </c>
       <c r="E37" t="s">
-        <v>452</v>
+        <v>298</v>
       </c>
       <c r="F37" t="s">
         <v>298</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B38" t="s">
-        <v>411</v>
+        <v>456</v>
       </c>
       <c r="C38" t="s">
-        <v>412</v>
+        <v>315</v>
       </c>
       <c r="D38" t="s">
         <v>266</v>
       </c>
       <c r="E38" t="s">
-        <v>417</v>
+        <v>457</v>
       </c>
       <c r="F38" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B39" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="C39" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="D39" t="s">
         <v>266</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>463</v>
       </c>
       <c r="F39" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B40" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C40" t="s">
-        <v>291</v>
+        <v>468</v>
       </c>
       <c r="D40" t="s">
         <v>266</v>
       </c>
       <c r="E40" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="F40" t="s">
-        <v>298</v>
+        <v>470</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B41" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="C41" t="s">
-        <v>291</v>
+        <v>474</v>
       </c>
       <c r="D41" t="s">
         <v>266</v>
       </c>
       <c r="E41" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="F41" t="s">
-        <v>298</v>
+        <v>476</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="B42" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="C42" t="s">
-        <v>467</v>
+        <v>291</v>
       </c>
       <c r="D42" t="s">
         <v>266</v>
       </c>
       <c r="E42" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="F42" t="s">
         <v>298</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B43" t="s">
-        <v>425</v>
+        <v>483</v>
       </c>
       <c r="C43" t="s">
-        <v>338</v>
+        <v>484</v>
       </c>
       <c r="D43" t="s">
-        <v>471</v>
+        <v>266</v>
       </c>
       <c r="E43" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="F43" t="s">
-        <v>298</v>
+        <v>486</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="B44" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>440</v>
       </c>
       <c r="D44" t="s">
         <v>266</v>
       </c>
       <c r="E44" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="F44" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B45" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="C45" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D45" t="s">
         <v>266</v>
       </c>
       <c r="E45" t="s">
-        <v>481</v>
+        <v>298</v>
       </c>
       <c r="F45" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B46" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="C46" t="s">
-        <v>486</v>
+        <v>291</v>
       </c>
       <c r="D46" t="s">
         <v>266</v>
       </c>
       <c r="E46" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="F46" t="s">
-        <v>488</v>
+        <v>298</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B47" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C47" t="s">
         <v>291</v>
@@ -4285,36 +4408,220 @@
         <v>266</v>
       </c>
       <c r="E47" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F47" t="s">
-        <v>493</v>
+        <v>298</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="B48" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C48" t="s">
+        <v>501</v>
+      </c>
+      <c r="D48" t="s">
+        <v>266</v>
+      </c>
+      <c r="E48" t="s">
+        <v>502</v>
+      </c>
+      <c r="F48" t="s">
+        <v>298</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>504</v>
+      </c>
+      <c r="B49" t="s">
+        <v>453</v>
+      </c>
+      <c r="C49" t="s">
+        <v>338</v>
+      </c>
+      <c r="D49" t="s">
+        <v>394</v>
+      </c>
+      <c r="E49" t="s">
+        <v>505</v>
+      </c>
+      <c r="F49" t="s">
+        <v>298</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>507</v>
+      </c>
+      <c r="B50" t="s">
+        <v>508</v>
+      </c>
+      <c r="C50" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" t="s">
+        <v>266</v>
+      </c>
+      <c r="E50" t="s">
+        <v>441</v>
+      </c>
+      <c r="F50" t="s">
+        <v>509</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>511</v>
+      </c>
+      <c r="B51" t="s">
+        <v>512</v>
+      </c>
+      <c r="C51" t="s">
+        <v>315</v>
+      </c>
+      <c r="D51" t="s">
+        <v>266</v>
+      </c>
+      <c r="E51" t="s">
+        <v>513</v>
+      </c>
+      <c r="F51" t="s">
+        <v>514</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>516</v>
+      </c>
+      <c r="B52" t="s">
+        <v>517</v>
+      </c>
+      <c r="C52" t="s">
+        <v>518</v>
+      </c>
+      <c r="D52" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" t="s">
+        <v>519</v>
+      </c>
+      <c r="F52" t="s">
+        <v>520</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>522</v>
+      </c>
+      <c r="B53" t="s">
+        <v>523</v>
+      </c>
+      <c r="C53" t="s">
+        <v>524</v>
+      </c>
+      <c r="D53" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" t="s">
+        <v>525</v>
+      </c>
+      <c r="F53" t="s">
+        <v>526</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>528</v>
+      </c>
+      <c r="B54" t="s">
+        <v>529</v>
+      </c>
+      <c r="C54" t="s">
+        <v>291</v>
+      </c>
+      <c r="D54" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" t="s">
+        <v>530</v>
+      </c>
+      <c r="F54" t="s">
+        <v>531</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>533</v>
+      </c>
+      <c r="B55" t="s">
+        <v>534</v>
+      </c>
+      <c r="C55" t="s">
         <v>278</v>
       </c>
-      <c r="D48" t="s">
-        <v>266</v>
-      </c>
-      <c r="E48" t="s">
-        <v>497</v>
-      </c>
-      <c r="F48" t="s">
-        <v>498</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>499</v>
+      <c r="D55" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" t="s">
+        <v>535</v>
+      </c>
+      <c r="F55" t="s">
+        <v>536</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>538</v>
+      </c>
+      <c r="B56" t="s">
+        <v>539</v>
+      </c>
+      <c r="C56" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" t="s">
+        <v>298</v>
+      </c>
+      <c r="F56" t="s">
+        <v>298</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -4367,6 +4674,14 @@
     <hyperlink ref="H46" r:id="rId45"/>
     <hyperlink ref="H47" r:id="rId46"/>
     <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
